--- a/pipeline/credit_rating/output/saigonratings_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20261027.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -640,7 +640,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -841,7 +841,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -983,7 +983,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -14960,7 +14960,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15567,7 +15567,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15701,7 +15701,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16505,7 +16505,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17175,7 +17175,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17577,7 +17577,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17711,7 +17711,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17912,7 +17912,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18046,7 +18046,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18247,7 +18247,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19386,7 +19386,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19453,7 +19453,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19587,7 +19587,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19721,7 +19721,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20056,7 +20056,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20123,7 +20123,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20257,7 +20257,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20391,7 +20391,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20458,7 +20458,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20592,7 +20592,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20793,7 +20793,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20860,7 +20860,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21061,7 +21061,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21195,7 +21195,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21262,7 +21262,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21463,7 +21463,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21664,7 +21664,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21731,7 +21731,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21865,7 +21865,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -21999,7 +21999,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22133,7 +22133,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22200,7 +22200,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22267,7 +22267,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22401,7 +22401,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S327" s="1" t="n">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S328" s="1" t="n">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S329" s="1" t="n">
@@ -22669,7 +22669,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S330" s="1" t="n">
@@ -22736,7 +22736,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S331" s="1" t="n">
@@ -22803,7 +22803,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S332" s="1" t="n">
@@ -22870,7 +22870,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S333" s="1" t="n">
@@ -22937,7 +22937,7 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S334" s="1" t="n">
@@ -23004,7 +23004,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S335" s="1" t="n">
@@ -23071,7 +23071,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S336" s="1" t="n">
@@ -23138,7 +23138,7 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S337" s="1" t="n">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S338" s="1" t="n">
@@ -23272,7 +23272,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S339" s="1" t="n">
@@ -23339,7 +23339,7 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S340" s="1" t="n">
@@ -23406,7 +23406,7 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S341" s="1" t="n">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S342" s="1" t="n">
@@ -23540,7 +23540,7 @@
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S343" s="1" t="n">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S344" s="1" t="n">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S345" s="1" t="n">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S346" s="1" t="n">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S347" s="1" t="n">
@@ -23875,7 +23875,7 @@
       </c>
       <c r="R348" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S348" s="1" t="n">
@@ -23942,7 +23942,7 @@
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S349" s="1" t="n">
@@ -24009,7 +24009,7 @@
       </c>
       <c r="R350" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S350" s="1" t="n">
@@ -24076,7 +24076,7 @@
       </c>
       <c r="R351" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S351" s="1" t="n">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="R352" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S352" s="1" t="n">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="R353" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S353" s="1" t="n">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S354" s="1" t="n">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S355" s="1" t="n">
@@ -24395,7 +24395,7 @@
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S356" t="inlineStr"/>
@@ -24444,7 +24444,7 @@
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S357" t="inlineStr"/>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S358" t="inlineStr"/>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>2026-10-27 02:34:02</t>
+          <t>2026-10-27 02:39:48</t>
         </is>
       </c>
       <c r="S359" t="inlineStr"/>

--- a/pipeline/credit_rating/output/saigonratings_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20261027.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -640,7 +640,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -841,7 +841,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -983,7 +983,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -14960,7 +14960,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15567,7 +15567,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15701,7 +15701,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16505,7 +16505,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17175,7 +17175,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17577,7 +17577,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17711,7 +17711,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17912,7 +17912,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18046,7 +18046,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18247,7 +18247,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19386,7 +19386,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19453,7 +19453,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19587,7 +19587,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19721,7 +19721,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20056,7 +20056,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20123,7 +20123,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20257,7 +20257,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20391,7 +20391,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20458,7 +20458,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20592,7 +20592,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20793,7 +20793,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20860,7 +20860,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21061,7 +21061,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21195,7 +21195,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21262,7 +21262,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21463,7 +21463,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21664,7 +21664,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21731,7 +21731,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21865,7 +21865,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -21999,7 +21999,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22133,7 +22133,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22200,7 +22200,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22267,7 +22267,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22401,7 +22401,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S327" s="1" t="n">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S328" s="1" t="n">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S329" s="1" t="n">
@@ -22669,7 +22669,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S330" s="1" t="n">
@@ -22736,7 +22736,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S331" s="1" t="n">
@@ -22803,7 +22803,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S332" s="1" t="n">
@@ -22870,7 +22870,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S333" s="1" t="n">
@@ -22937,7 +22937,7 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S334" s="1" t="n">
@@ -23004,7 +23004,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S335" s="1" t="n">
@@ -23071,7 +23071,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S336" s="1" t="n">
@@ -23138,7 +23138,7 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S337" s="1" t="n">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S338" s="1" t="n">
@@ -23272,7 +23272,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S339" s="1" t="n">
@@ -23339,7 +23339,7 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S340" s="1" t="n">
@@ -23406,7 +23406,7 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S341" s="1" t="n">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S342" s="1" t="n">
@@ -23540,7 +23540,7 @@
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S343" s="1" t="n">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S344" s="1" t="n">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S345" s="1" t="n">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S346" s="1" t="n">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S347" s="1" t="n">
@@ -23875,7 +23875,7 @@
       </c>
       <c r="R348" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S348" s="1" t="n">
@@ -23942,7 +23942,7 @@
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S349" s="1" t="n">
@@ -24009,7 +24009,7 @@
       </c>
       <c r="R350" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S350" s="1" t="n">
@@ -24076,7 +24076,7 @@
       </c>
       <c r="R351" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S351" s="1" t="n">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="R352" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S352" s="1" t="n">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="R353" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S353" s="1" t="n">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S354" s="1" t="n">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S355" s="1" t="n">
@@ -24395,7 +24395,7 @@
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S356" t="inlineStr"/>
@@ -24444,7 +24444,7 @@
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S357" t="inlineStr"/>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S358" t="inlineStr"/>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>2026-10-27 02:39:48</t>
+          <t>2026-10-27 09:18:22</t>
         </is>
       </c>
       <c r="S359" t="inlineStr"/>

--- a/pipeline/credit_rating/output/saigonratings_xhtn_20261027.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20261027.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -640,7 +640,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -841,7 +841,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -983,7 +983,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -14960,7 +14960,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15567,7 +15567,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15634,7 +15634,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15701,7 +15701,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16505,7 +16505,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17175,7 +17175,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17577,7 +17577,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17711,7 +17711,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17912,7 +17912,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18046,7 +18046,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18247,7 +18247,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19386,7 +19386,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19453,7 +19453,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19587,7 +19587,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19721,7 +19721,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20056,7 +20056,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20123,7 +20123,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20190,7 +20190,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20257,7 +20257,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20391,7 +20391,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20458,7 +20458,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20592,7 +20592,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20793,7 +20793,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20860,7 +20860,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -20994,7 +20994,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21061,7 +21061,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21195,7 +21195,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21262,7 +21262,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21396,7 +21396,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21463,7 +21463,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21664,7 +21664,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21731,7 +21731,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21865,7 +21865,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -21999,7 +21999,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22133,7 +22133,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22200,7 +22200,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22267,7 +22267,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22401,7 +22401,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S327" s="1" t="n">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S328" s="1" t="n">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S329" s="1" t="n">
@@ -22669,7 +22669,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S330" s="1" t="n">
@@ -22736,7 +22736,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S331" s="1" t="n">
@@ -22803,7 +22803,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S332" s="1" t="n">
@@ -22870,7 +22870,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S333" s="1" t="n">
@@ -22937,7 +22937,7 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S334" s="1" t="n">
@@ -23004,7 +23004,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S335" s="1" t="n">
@@ -23071,7 +23071,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S336" s="1" t="n">
@@ -23138,7 +23138,7 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S337" s="1" t="n">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S338" s="1" t="n">
@@ -23272,7 +23272,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S339" s="1" t="n">
@@ -23339,7 +23339,7 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S340" s="1" t="n">
@@ -23406,7 +23406,7 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S341" s="1" t="n">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S342" s="1" t="n">
@@ -23540,7 +23540,7 @@
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S343" s="1" t="n">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S344" s="1" t="n">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S345" s="1" t="n">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S346" s="1" t="n">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S347" s="1" t="n">
@@ -23875,7 +23875,7 @@
       </c>
       <c r="R348" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S348" s="1" t="n">
@@ -23942,7 +23942,7 @@
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S349" s="1" t="n">
@@ -24009,7 +24009,7 @@
       </c>
       <c r="R350" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S350" s="1" t="n">
@@ -24076,7 +24076,7 @@
       </c>
       <c r="R351" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S351" s="1" t="n">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="R352" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S352" s="1" t="n">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="R353" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S353" s="1" t="n">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S354" s="1" t="n">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S355" s="1" t="n">
@@ -24395,7 +24395,7 @@
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S356" t="inlineStr"/>
@@ -24444,7 +24444,7 @@
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S357" t="inlineStr"/>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S358" t="inlineStr"/>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>2026-10-27 09:18:22</t>
+          <t>2026-10-27 14:51:03</t>
         </is>
       </c>
       <c r="S359" t="inlineStr"/>
